--- a/input/timetable/Магистратура_Экономика.xlsx
+++ b/input/timetable/Магистратура_Экономика.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="83">
   <si>
     <t>пара</t>
   </si>
@@ -71,6 +71,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -110,12 +113,24 @@
     <t>Практикум по межкультурной коммуникации (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Масюк Н.А.</t>
+  </si>
+  <si>
     <t>Экономика фирмы (пр), ЭОиДОТ</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>Тимофеева Н.В.</t>
+  </si>
+  <si>
+    <t>Грамма Д.В.</t>
+  </si>
+  <si>
+    <t>Иванова Е.А.</t>
+  </si>
+  <si>
     <t>История и методология науки (лек 16 ч)</t>
   </si>
   <si>
@@ -126,6 +141,9 @@
   </si>
   <si>
     <t>Экономический анализ (продвинутый курс) (лек), ЭОиДОТ//  Бизнес-планирование (лек), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Зубарева Л.В./Селюков М.В.</t>
   </si>
   <si>
     <t>День самостоятельной работы</t>
@@ -187,12 +205,18 @@
     <t>Финансовая диагностика и контроль хозяйственной деятельности (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Прокопьева Т.В.</t>
+  </si>
+  <si>
     <t>Финансовая диагностика и контроль хозяйственной деятельности (пр), ЭОиДОТ</t>
   </si>
   <si>
     <t>Основы управления рисками в организации (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Иванов С.В.</t>
+  </si>
+  <si>
     <t>Корпоративное управление (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -211,9 +235,18 @@
     <t>Корпоративное управление (пр), ЭОиДОТ// Современные технологии презентаций и бизнес-коммуникаций (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Масюк Н.А./Шутро Е.Н.</t>
+  </si>
+  <si>
+    <t>Бутенко Н.А.</t>
+  </si>
+  <si>
     <t>История и методология науки (пр),ЭОиДОТ // Институциональные аспекты ведения бизнеса в России (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Бутенко Н.А./Каратаев А.С.</t>
+  </si>
+  <si>
     <t>Экономика фирмы (лек), ЭОиДОТ// Институциональные аспекты ведения бизнеса в России (пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -223,6 +256,12 @@
     <t>Бизнес-аналитика (пр), ЭОиДОТ// Теория и практика формирования рыночной стратегии (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Галюта О.Н./Фейзуллаев М.А.</t>
+  </si>
+  <si>
+    <t>Галюта О.Н./Каратаева Г.Е.</t>
+  </si>
+  <si>
     <t>Прикладная эконометрика и анализ больших данных в экономике (лек 24 ч), ЭОиДОТ</t>
   </si>
   <si>
@@ -235,13 +274,28 @@
     <t>Иностранный язык в профессиональной сфере (лек), ЭОиДОТ//</t>
   </si>
   <si>
+    <t>Шутро Е.Н.</t>
+  </si>
+  <si>
     <t>Основы управления рисками в организации (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Афанасьев С.А./Селюков М.В.</t>
+  </si>
+  <si>
+    <t>Афанасьев С.А</t>
+  </si>
+  <si>
     <t>ФТД:  Публичная нефинансовая отчетность (лек), ЭОиДОТ// Основы научных исследований в области экономики и управления (лек), ЭОиДОТ</t>
   </si>
   <si>
     <t>ФТД:  Публичная нефинансовая отчетность (пр), ЭОиДОТ// Основы научных исследований в области экономики и управления (пр), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Цыкура М.Г./Каратаева Г.Е.</t>
+  </si>
+  <si>
+    <t>Сукиасян А.Г.</t>
   </si>
 </sst>
 </file>
@@ -342,7 +396,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,8 +413,14 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="40">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -449,6 +509,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -694,6 +767,21 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -883,7 +971,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -926,228 +1014,237 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -1477,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1486,113 +1583,115 @@
     <col min="4" max="4" width="19" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20" style="2" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="H2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="I4" s="5"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J4" s="5"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="11" t="s">
+      <c r="J5" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="9"/>
+      <c r="L5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -1601,71 +1700,71 @@
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="J6" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="13"/>
+      <c r="L6" s="10">
+        <v>1</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A7" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="10">
-        <v>1</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7" s="12" t="s">
-        <v>16</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="16" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="14" t="s">
+      <c r="H7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="17" t="s">
+      <c r="K7" s="15"/>
+      <c r="L7" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="95" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="95" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="95"/>
-      <c r="L8" s="95"/>
-    </row>
-    <row r="9" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="H8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+    </row>
+    <row r="9" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>0</v>
@@ -1676,508 +1775,580 @@
       <c r="D9" s="21"/>
       <c r="E9" s="22"/>
       <c r="F9" s="23"/>
-      <c r="G9" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="19" t="s">
+      <c r="G9" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="J9" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="23"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A10" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="39">
+      <c r="K9" s="21"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A10" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="45">
         <v>6</v>
       </c>
-      <c r="C10" s="64"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="25">
+      <c r="C10" s="85"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="26">
         <v>6</v>
       </c>
-      <c r="I10" s="64"/>
-      <c r="J10" s="65"/>
-      <c r="K10" s="65"/>
-      <c r="L10" s="66"/>
-    </row>
-    <row r="11" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="43"/>
-      <c r="B11" s="40">
+      <c r="J10" s="85"/>
+      <c r="K10" s="86"/>
+      <c r="L10" s="86"/>
+      <c r="M10" s="87"/>
+      <c r="N10" s="32"/>
+    </row>
+    <row r="11" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="49"/>
+      <c r="B11" s="46">
         <v>7</v>
       </c>
-      <c r="C11" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="27">
+      <c r="C11" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="27"/>
+      <c r="I11" s="28">
         <v>7</v>
       </c>
-      <c r="I11" s="100" t="s">
+      <c r="J11" s="88" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="89"/>
+      <c r="L11" s="89"/>
+      <c r="M11" s="90"/>
+      <c r="N11" s="40" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="50"/>
+      <c r="B12" s="53">
+        <v>8</v>
+      </c>
+      <c r="C12" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="101"/>
-      <c r="K11" s="101"/>
-      <c r="L11" s="102"/>
-    </row>
-    <row r="12" spans="1:12" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="44"/>
-      <c r="B12" s="47">
+      <c r="H12" s="29"/>
+      <c r="I12" s="30">
         <v>8</v>
       </c>
-      <c r="C12" s="70" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29">
+      <c r="J12" s="91" t="s">
+        <v>68</v>
+      </c>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="41" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A13" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="54">
+        <v>6</v>
+      </c>
+      <c r="C13" s="94"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="26">
+        <v>6</v>
+      </c>
+      <c r="J13" s="94"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="95"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="32"/>
+    </row>
+    <row r="14" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="49"/>
+      <c r="B14" s="46">
+        <v>7</v>
+      </c>
+      <c r="C14" s="70" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="27"/>
+      <c r="I14" s="28">
+        <v>7</v>
+      </c>
+      <c r="J14" s="70" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="71"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="52"/>
+      <c r="B15" s="53">
         <v>8</v>
       </c>
-      <c r="I12" s="103" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="105"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A13" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="48">
-        <v>6</v>
-      </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="25">
-        <v>6</v>
-      </c>
-      <c r="I13" s="73"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="75"/>
-    </row>
-    <row r="14" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="43"/>
-      <c r="B14" s="40">
-        <v>7</v>
-      </c>
-      <c r="C14" s="67" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="27">
-        <v>7</v>
-      </c>
-      <c r="I14" s="67" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="69"/>
-    </row>
-    <row r="15" spans="1:12" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="46"/>
-      <c r="B15" s="47">
+      <c r="C15" s="107" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="33"/>
+      <c r="I15" s="30">
         <v>8</v>
       </c>
-      <c r="C15" s="76" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="29">
-        <v>8</v>
-      </c>
-      <c r="I15" s="70" t="s">
-        <v>56</v>
-      </c>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="72"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A16" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="48">
+      <c r="J15" s="76" t="s">
+        <v>67</v>
+      </c>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="78"/>
+      <c r="N15" s="41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A16" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="54">
         <v>6</v>
       </c>
       <c r="C16" s="79"/>
       <c r="D16" s="80"/>
       <c r="E16" s="80"/>
       <c r="F16" s="81"/>
-      <c r="G16" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="25">
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="26">
         <v>6</v>
       </c>
-      <c r="I16" s="79"/>
-      <c r="J16" s="80"/>
+      <c r="J16" s="79"/>
       <c r="K16" s="80"/>
-      <c r="L16" s="81"/>
-    </row>
-    <row r="17" spans="1:16" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="43"/>
-      <c r="B17" s="40">
+      <c r="L16" s="80"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="32"/>
+    </row>
+    <row r="17" spans="1:18" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="49"/>
+      <c r="B17" s="46">
         <v>7</v>
       </c>
-      <c r="C17" s="67" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="27">
+      <c r="C17" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="27"/>
+      <c r="I17" s="28">
         <v>7</v>
       </c>
-      <c r="I17" s="67" t="s">
-        <v>54</v>
-      </c>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="69"/>
-    </row>
-    <row r="18" spans="1:16" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="46"/>
-      <c r="B18" s="47">
+      <c r="J17" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="52"/>
+      <c r="B18" s="53">
         <v>8</v>
       </c>
-      <c r="C18" s="70" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="29">
+      <c r="C18" s="76" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" s="33"/>
+      <c r="I18" s="30">
         <v>8</v>
       </c>
-      <c r="I18" s="67" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="69"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A19" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="48">
+      <c r="J18" s="70" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" s="71"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A19" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="54">
         <v>6</v>
       </c>
       <c r="C19" s="82"/>
       <c r="D19" s="83"/>
       <c r="E19" s="83"/>
       <c r="F19" s="84"/>
-      <c r="G19" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="25">
+      <c r="G19" s="32"/>
+      <c r="H19" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="26">
         <v>6</v>
       </c>
-      <c r="I19" s="82"/>
-      <c r="J19" s="83"/>
+      <c r="J19" s="82"/>
       <c r="K19" s="83"/>
-      <c r="L19" s="84"/>
-    </row>
-    <row r="20" spans="1:16" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="43"/>
-      <c r="B20" s="40">
+      <c r="L19" s="83"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="32"/>
+    </row>
+    <row r="20" spans="1:18" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="49"/>
+      <c r="B20" s="46">
         <v>7</v>
       </c>
-      <c r="C20" s="67" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="32">
+      <c r="C20" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="27"/>
+      <c r="I20" s="34">
         <v>7</v>
       </c>
-      <c r="I20" s="67" t="s">
-        <v>55</v>
-      </c>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="69"/>
-      <c r="P20" s="2" t="s">
+      <c r="J20" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="K20" s="71"/>
+      <c r="L20" s="71"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="52"/>
+      <c r="B21" s="53">
+        <v>8</v>
+      </c>
+      <c r="C21" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="41" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="46"/>
-      <c r="B21" s="47">
+      <c r="H21" s="33"/>
+      <c r="I21" s="35">
         <v>8</v>
       </c>
-      <c r="C21" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="33">
-        <v>8</v>
-      </c>
-      <c r="I21" s="91" t="s">
-        <v>29</v>
-      </c>
-      <c r="J21" s="92"/>
-      <c r="K21" s="92"/>
-      <c r="L21" s="93"/>
-    </row>
-    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="48">
+      <c r="J21" s="100" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" s="101"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="102"/>
+      <c r="N21" s="41" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="54">
         <v>6</v>
       </c>
       <c r="C22" s="79"/>
       <c r="D22" s="80"/>
       <c r="E22" s="80"/>
       <c r="F22" s="81"/>
-      <c r="G22" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="25">
+      <c r="G22" s="32"/>
+      <c r="H22" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" s="26">
         <v>6</v>
       </c>
-      <c r="I22" s="79"/>
-      <c r="J22" s="80"/>
+      <c r="J22" s="79"/>
       <c r="K22" s="80"/>
-      <c r="L22" s="81"/>
-    </row>
-    <row r="23" spans="1:16" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="38"/>
-      <c r="B23" s="40">
+      <c r="L22" s="80"/>
+      <c r="M22" s="81"/>
+      <c r="N22" s="32"/>
+    </row>
+    <row r="23" spans="1:18" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="44"/>
+      <c r="B23" s="46">
         <v>7</v>
       </c>
-      <c r="C23" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="27">
+      <c r="C23" s="70" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" s="36"/>
+      <c r="I23" s="28">
         <v>7</v>
       </c>
-      <c r="I23" s="67" t="s">
+      <c r="J23" s="70" t="s">
+        <v>79</v>
+      </c>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="40" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="56"/>
+      <c r="B24" s="55">
+        <v>8</v>
+      </c>
+      <c r="C24" s="70" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" s="37"/>
+      <c r="I24" s="30">
+        <v>8</v>
+      </c>
+      <c r="J24" s="100" t="s">
+        <v>80</v>
+      </c>
+      <c r="K24" s="101"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="102"/>
+      <c r="N24" s="41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A25" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="60">
+        <v>1</v>
+      </c>
+      <c r="C25" s="110" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="45"/>
+      <c r="J25" s="69" t="s">
+        <v>41</v>
+      </c>
+      <c r="K25" s="69"/>
+      <c r="L25" s="69"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="42"/>
+    </row>
+    <row r="26" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="57"/>
+      <c r="B26" s="61">
+        <v>2</v>
+      </c>
+      <c r="C26" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="64"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="103"/>
+      <c r="L26" s="103"/>
+      <c r="M26" s="103"/>
+      <c r="N26" s="40"/>
+    </row>
+    <row r="27" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="57"/>
+      <c r="B27" s="61">
+        <v>3</v>
+      </c>
+      <c r="C27" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" s="64"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="72"/>
+      <c r="N27" s="40"/>
+    </row>
+    <row r="28" spans="1:18" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="58"/>
+      <c r="B28" s="61">
+        <v>4</v>
+      </c>
+      <c r="C28" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="98"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="H28" s="65"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="71"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="40"/>
+    </row>
+    <row r="29" spans="1:18" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="59"/>
+      <c r="B29" s="62">
+        <v>5</v>
+      </c>
+      <c r="C29" s="104" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" s="66"/>
+      <c r="I29" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="J29" s="73" t="s">
+        <v>36</v>
+      </c>
+      <c r="K29" s="74"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="75"/>
+      <c r="N29" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="J23" s="68"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="69"/>
-    </row>
-    <row r="24" spans="1:16" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="50"/>
-      <c r="B24" s="49">
-        <v>8</v>
-      </c>
-      <c r="C24" s="67" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="29">
-        <v>8</v>
-      </c>
-      <c r="I24" s="91" t="s">
-        <v>64</v>
-      </c>
-      <c r="J24" s="92"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="93"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A25" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="54">
-        <v>1</v>
-      </c>
-      <c r="C25" s="85" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="H25" s="39"/>
-      <c r="I25" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="J25" s="96"/>
-      <c r="K25" s="96"/>
-      <c r="L25" s="96"/>
-    </row>
-    <row r="26" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="51"/>
-      <c r="B26" s="55">
-        <v>2</v>
-      </c>
-      <c r="C26" s="88" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="94"/>
-      <c r="J26" s="94"/>
-      <c r="K26" s="94"/>
-      <c r="L26" s="94"/>
-    </row>
-    <row r="27" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="51"/>
-      <c r="B27" s="55">
-        <v>3</v>
-      </c>
-      <c r="C27" s="88" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="68"/>
-      <c r="K27" s="68"/>
-      <c r="L27" s="69"/>
-    </row>
-    <row r="28" spans="1:16" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="52"/>
-      <c r="B28" s="55">
-        <v>4</v>
-      </c>
-      <c r="C28" s="88" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="68"/>
-      <c r="K28" s="68"/>
-      <c r="L28" s="69"/>
-    </row>
-    <row r="29" spans="1:16" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="53"/>
-      <c r="B29" s="56">
-        <v>5</v>
-      </c>
-      <c r="C29" s="61" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="97" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" s="98"/>
-      <c r="K29" s="98"/>
-      <c r="L29" s="99"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="K31" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C11:F11"/>
@@ -2194,13 +2365,39 @@
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="C21:F21"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6 I6"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 K5">
+    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6 J6"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 L5">
       <formula1>"осенний, весенний"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5 I5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5 J5">
       <formula1>"2025-2026"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2221,7 +2418,7 @@
             <xm:f>IF('\Users\grn.adm\Desktop\[Пример.xlsx]Лист2'!#REF!=0,"",'\Users\grn.adm\Desktop\[Пример.xlsx]Лист2'!#REF!)</xm:f>
             <x14:dxf/>
           </x14:cfRule>
-          <xm:sqref>I8</xm:sqref>
+          <xm:sqref>J8</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
